--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120441204</v>
+        <v>120438911</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528648</v>
+        <v>528508</v>
       </c>
       <c r="R9" t="n">
-        <v>6937685</v>
+        <v>6937667</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120440905</v>
+        <v>120438845</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528612</v>
+        <v>528539</v>
       </c>
       <c r="R10" t="n">
-        <v>6937706</v>
+        <v>6937680</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120440965</v>
+        <v>120441204</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528632</v>
+        <v>528648</v>
       </c>
       <c r="R11" t="n">
-        <v>6937690</v>
+        <v>6937685</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120440848</v>
+        <v>120440905</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528571</v>
+        <v>528612</v>
       </c>
       <c r="R12" t="n">
-        <v>6937738</v>
+        <v>6937706</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120438911</v>
+        <v>120440965</v>
       </c>
       <c r="B13" t="n">
         <v>90864</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528508</v>
+        <v>528632</v>
       </c>
       <c r="R13" t="n">
-        <v>6937667</v>
+        <v>6937690</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120438845</v>
+        <v>120440848</v>
       </c>
       <c r="B14" t="n">
         <v>90864</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528539</v>
+        <v>528571</v>
       </c>
       <c r="R14" t="n">
-        <v>6937680</v>
+        <v>6937738</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120440938</v>
+        <v>120441284</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528625</v>
+        <v>528669</v>
       </c>
       <c r="R22" t="n">
-        <v>6937678</v>
+        <v>6937668</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120441284</v>
+        <v>120440938</v>
       </c>
       <c r="B23" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528669</v>
+        <v>528625</v>
       </c>
       <c r="R23" t="n">
-        <v>6937668</v>
+        <v>6937678</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120439210</v>
+        <v>120437120</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>78279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528515</v>
+        <v>528870</v>
       </c>
       <c r="R24" t="n">
-        <v>6937709</v>
+        <v>6937526</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120437120</v>
+        <v>120439814</v>
       </c>
       <c r="B25" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528870</v>
+        <v>528443</v>
       </c>
       <c r="R25" t="n">
-        <v>6937526</v>
+        <v>6937793</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120439814</v>
+        <v>120439210</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528443</v>
+        <v>528515</v>
       </c>
       <c r="R26" t="n">
-        <v>6937793</v>
+        <v>6937709</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120436879</v>
+        <v>120439353</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,37 +3251,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528950</v>
+        <v>528525</v>
       </c>
       <c r="R27" t="n">
-        <v>6937556</v>
+        <v>6937692</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3337,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120438576</v>
+        <v>120436879</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528646</v>
+        <v>528950</v>
       </c>
       <c r="R28" t="n">
-        <v>6937603</v>
+        <v>6937556</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3439,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120440885</v>
+        <v>120438576</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3460,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,13 +3484,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528599</v>
+        <v>528646</v>
       </c>
       <c r="R29" t="n">
-        <v>6937706</v>
+        <v>6937603</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3541,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120439353</v>
+        <v>120440885</v>
       </c>
       <c r="B30" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,42 +3562,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528525</v>
+        <v>528599</v>
       </c>
       <c r="R30" t="n">
-        <v>6937692</v>
+        <v>6937706</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120441974</v>
+        <v>120439563</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528835</v>
+        <v>528498</v>
       </c>
       <c r="R33" t="n">
-        <v>6937628</v>
+        <v>6937745</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120439563</v>
+        <v>120439368</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>90591</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3966,25 +3966,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528498</v>
+        <v>528518</v>
       </c>
       <c r="R34" t="n">
-        <v>6937745</v>
+        <v>6937705</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120439368</v>
+        <v>120441974</v>
       </c>
       <c r="B36" t="n">
-        <v>90591</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528518</v>
+        <v>528835</v>
       </c>
       <c r="R36" t="n">
-        <v>6937705</v>
+        <v>6937628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120441538</v>
+        <v>120440130</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528764</v>
+        <v>528413</v>
       </c>
       <c r="R52" t="n">
-        <v>6937612</v>
+        <v>6937790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120440130</v>
+        <v>120441538</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528413</v>
+        <v>528764</v>
       </c>
       <c r="R53" t="n">
-        <v>6937790</v>
+        <v>6937612</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120441600</v>
+        <v>120441387</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528802</v>
+        <v>528685</v>
       </c>
       <c r="R2" t="n">
-        <v>6937600</v>
+        <v>6937650</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120441265</v>
+        <v>120438560</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528650</v>
+        <v>528656</v>
       </c>
       <c r="R3" t="n">
-        <v>6937679</v>
+        <v>6937598</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120438542</v>
+        <v>120441066</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528659</v>
+        <v>528637</v>
       </c>
       <c r="R4" t="n">
-        <v>6937599</v>
+        <v>6937690</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120439192</v>
+        <v>120439035</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528507</v>
+        <v>528498</v>
       </c>
       <c r="R5" t="n">
-        <v>6937699</v>
+        <v>6937681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120438876</v>
+        <v>120437120</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528532</v>
+        <v>528870</v>
       </c>
       <c r="R6" t="n">
-        <v>6937674</v>
+        <v>6937526</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120439057</v>
+        <v>120440965</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528492</v>
+        <v>528632</v>
       </c>
       <c r="R7" t="n">
-        <v>6937685</v>
+        <v>6937690</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120441461</v>
+        <v>120437608</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,46 +1304,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528743</v>
+        <v>528744</v>
       </c>
       <c r="R8" t="n">
-        <v>6937610</v>
+        <v>6937574</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120438911</v>
+        <v>120440885</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528508</v>
+        <v>528599</v>
       </c>
       <c r="R9" t="n">
-        <v>6937667</v>
+        <v>6937706</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120438845</v>
+        <v>120441600</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528539</v>
+        <v>528802</v>
       </c>
       <c r="R10" t="n">
-        <v>6937680</v>
+        <v>6937600</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120441204</v>
+        <v>120438542</v>
       </c>
       <c r="B11" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528648</v>
+        <v>528659</v>
       </c>
       <c r="R11" t="n">
-        <v>6937685</v>
+        <v>6937599</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120440905</v>
+        <v>120439129</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528612</v>
+        <v>528507</v>
       </c>
       <c r="R12" t="n">
-        <v>6937706</v>
+        <v>6937686</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120440965</v>
+        <v>120440054</v>
       </c>
       <c r="B13" t="n">
-        <v>90864</v>
+        <v>90972</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1818,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528632</v>
+        <v>528395</v>
       </c>
       <c r="R13" t="n">
-        <v>6937690</v>
+        <v>6937798</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120440848</v>
+        <v>120441265</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528571</v>
+        <v>528650</v>
       </c>
       <c r="R14" t="n">
-        <v>6937738</v>
+        <v>6937679</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120437190</v>
+        <v>120439210</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528854</v>
+        <v>528515</v>
       </c>
       <c r="R15" t="n">
-        <v>6937530</v>
+        <v>6937709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120437570</v>
+        <v>120439149</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528747</v>
+        <v>528506</v>
       </c>
       <c r="R16" t="n">
-        <v>6937557</v>
+        <v>6937698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120440419</v>
+        <v>120438576</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528464</v>
+        <v>528646</v>
       </c>
       <c r="R17" t="n">
-        <v>6937744</v>
+        <v>6937603</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120439870</v>
+        <v>120440522</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528452</v>
+        <v>528469</v>
       </c>
       <c r="R18" t="n">
-        <v>6937837</v>
+        <v>6937757</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120437716</v>
+        <v>120440400</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528697</v>
+        <v>528463</v>
       </c>
       <c r="R19" t="n">
-        <v>6937605</v>
+        <v>6937740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120437608</v>
+        <v>120436956</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528744</v>
+        <v>528924</v>
       </c>
       <c r="R20" t="n">
-        <v>6937574</v>
+        <v>6937549</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120440522</v>
+        <v>120441204</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528469</v>
+        <v>528648</v>
       </c>
       <c r="R21" t="n">
-        <v>6937757</v>
+        <v>6937685</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120441284</v>
+        <v>120438853</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528669</v>
+        <v>528547</v>
       </c>
       <c r="R22" t="n">
-        <v>6937668</v>
+        <v>6937670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120440938</v>
+        <v>120437570</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528625</v>
+        <v>528747</v>
       </c>
       <c r="R23" t="n">
-        <v>6937678</v>
+        <v>6937557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120437120</v>
+        <v>120438646</v>
       </c>
       <c r="B24" t="n">
-        <v>78279</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528870</v>
+        <v>528617</v>
       </c>
       <c r="R24" t="n">
-        <v>6937526</v>
+        <v>6937594</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3031,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120439814</v>
+        <v>120439384</v>
       </c>
       <c r="B25" t="n">
         <v>79623</v>
@@ -3071,13 +3061,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528443</v>
+        <v>528516</v>
       </c>
       <c r="R25" t="n">
-        <v>6937793</v>
+        <v>6937699</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120439210</v>
+        <v>120441284</v>
       </c>
       <c r="B26" t="n">
         <v>90864</v>
@@ -3173,13 +3163,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528515</v>
+        <v>528669</v>
       </c>
       <c r="R26" t="n">
-        <v>6937709</v>
+        <v>6937668</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120439353</v>
+        <v>120441461</v>
       </c>
       <c r="B27" t="n">
         <v>57473</v>
@@ -3280,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528525</v>
+        <v>528743</v>
       </c>
       <c r="R27" t="n">
-        <v>6937692</v>
+        <v>6937610</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3342,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120436879</v>
+        <v>120439814</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3382,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528950</v>
+        <v>528443</v>
       </c>
       <c r="R28" t="n">
-        <v>6937556</v>
+        <v>6937793</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3444,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120438576</v>
+        <v>120441687</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3484,13 +3474,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528646</v>
+        <v>528832</v>
       </c>
       <c r="R29" t="n">
-        <v>6937603</v>
+        <v>6937620</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3546,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120440885</v>
+        <v>120440774</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,13 +3576,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528599</v>
+        <v>528513</v>
       </c>
       <c r="R30" t="n">
-        <v>6937706</v>
+        <v>6937754</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3648,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120438833</v>
+        <v>120439601</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528539</v>
+        <v>528477</v>
       </c>
       <c r="R31" t="n">
-        <v>6937677</v>
+        <v>6937781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120439804</v>
+        <v>120439057</v>
       </c>
       <c r="B32" t="n">
-        <v>90141</v>
+        <v>5169</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3762,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>937</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528450</v>
+        <v>528492</v>
       </c>
       <c r="R32" t="n">
-        <v>6937792</v>
+        <v>6937685</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3826,6 +3816,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3852,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120439563</v>
+        <v>120441274</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3864,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528498</v>
+        <v>528669</v>
       </c>
       <c r="R33" t="n">
-        <v>6937745</v>
+        <v>6937672</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3954,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120439368</v>
+        <v>120437716</v>
       </c>
       <c r="B34" t="n">
-        <v>90591</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3966,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528518</v>
+        <v>528697</v>
       </c>
       <c r="R34" t="n">
-        <v>6937705</v>
+        <v>6937605</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120439035</v>
+        <v>120439353</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,41 +4063,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528498</v>
+        <v>528525</v>
       </c>
       <c r="R35" t="n">
-        <v>6937681</v>
+        <v>6937692</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4132,11 +4132,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4163,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120441974</v>
+        <v>120440938</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4174,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528835</v>
+        <v>528625</v>
       </c>
       <c r="R36" t="n">
-        <v>6937628</v>
+        <v>6937678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120439601</v>
+        <v>120439368</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>90591</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4272,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528477</v>
+        <v>528518</v>
       </c>
       <c r="R37" t="n">
-        <v>6937781</v>
+        <v>6937705</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120438963</v>
+        <v>120439870</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4374,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,13 +4402,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528506</v>
+        <v>528452</v>
       </c>
       <c r="R38" t="n">
-        <v>6937684</v>
+        <v>6937837</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4469,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120440104</v>
+        <v>120437507</v>
       </c>
       <c r="B39" t="n">
-        <v>90864</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4480,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,13 +4504,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528416</v>
+        <v>528761</v>
       </c>
       <c r="R39" t="n">
-        <v>6937802</v>
+        <v>6937549</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4571,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120440774</v>
+        <v>120438845</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4583,25 +4578,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528513</v>
+        <v>528539</v>
       </c>
       <c r="R40" t="n">
-        <v>6937754</v>
+        <v>6937680</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4673,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120438560</v>
+        <v>120441538</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4708,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528656</v>
+        <v>528764</v>
       </c>
       <c r="R41" t="n">
-        <v>6937598</v>
+        <v>6937612</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120437507</v>
+        <v>120440837</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528761</v>
+        <v>528564</v>
       </c>
       <c r="R42" t="n">
-        <v>6937549</v>
+        <v>6937735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120436956</v>
+        <v>120438265</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,21 +4888,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,13 +4912,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528924</v>
+        <v>528695</v>
       </c>
       <c r="R43" t="n">
-        <v>6937549</v>
+        <v>6937599</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120438853</v>
+        <v>120437190</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4991,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,13 +5014,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528547</v>
+        <v>528854</v>
       </c>
       <c r="R44" t="n">
-        <v>6937670</v>
+        <v>6937530</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120441274</v>
+        <v>120440130</v>
       </c>
       <c r="B45" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528669</v>
+        <v>528413</v>
       </c>
       <c r="R45" t="n">
-        <v>6937672</v>
+        <v>6937790</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120439927</v>
+        <v>120441974</v>
       </c>
       <c r="B46" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5195,25 +5190,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,13 +5218,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528418</v>
+        <v>528835</v>
       </c>
       <c r="R46" t="n">
-        <v>6937810</v>
+        <v>6937628</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5285,7 +5280,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120441387</v>
+        <v>120439563</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5325,13 +5320,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528685</v>
+        <v>528498</v>
       </c>
       <c r="R47" t="n">
-        <v>6937650</v>
+        <v>6937745</v>
       </c>
       <c r="S47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5387,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120440400</v>
+        <v>120440905</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,13 +5422,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528463</v>
+        <v>528612</v>
       </c>
       <c r="R48" t="n">
-        <v>6937740</v>
+        <v>6937706</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5489,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120440837</v>
+        <v>120440848</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,13 +5524,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528564</v>
+        <v>528571</v>
       </c>
       <c r="R49" t="n">
-        <v>6937735</v>
+        <v>6937738</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5591,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120438265</v>
+        <v>120440104</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5602,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,13 +5626,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528695</v>
+        <v>528416</v>
       </c>
       <c r="R50" t="n">
-        <v>6937599</v>
+        <v>6937802</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5693,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120438646</v>
+        <v>120436879</v>
       </c>
       <c r="B51" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5704,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528617</v>
+        <v>528950</v>
       </c>
       <c r="R51" t="n">
-        <v>6937594</v>
+        <v>6937556</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5795,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120440130</v>
+        <v>120438876</v>
       </c>
       <c r="B52" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,13 +5830,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528413</v>
+        <v>528532</v>
       </c>
       <c r="R52" t="n">
-        <v>6937790</v>
+        <v>6937674</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5897,7 +5892,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120441538</v>
+        <v>120439192</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528764</v>
+        <v>528507</v>
       </c>
       <c r="R53" t="n">
-        <v>6937612</v>
+        <v>6937699</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120441687</v>
+        <v>120438911</v>
       </c>
       <c r="B54" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,13 +6034,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528832</v>
+        <v>528508</v>
       </c>
       <c r="R54" t="n">
-        <v>6937620</v>
+        <v>6937667</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6101,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120440054</v>
+        <v>120438963</v>
       </c>
       <c r="B55" t="n">
-        <v>90972</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,20 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528395</v>
+        <v>528506</v>
       </c>
       <c r="R55" t="n">
-        <v>6937798</v>
+        <v>6937684</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120439149</v>
+        <v>120439804</v>
       </c>
       <c r="B56" t="n">
-        <v>95478</v>
+        <v>90141</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>937</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,13 +6238,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528506</v>
+        <v>528450</v>
       </c>
       <c r="R56" t="n">
-        <v>6937698</v>
+        <v>6937792</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120439129</v>
+        <v>120439927</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6312,25 +6312,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528507</v>
+        <v>528418</v>
       </c>
       <c r="R57" t="n">
-        <v>6937686</v>
+        <v>6937810</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120439384</v>
+        <v>120440419</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6418,21 +6418,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528516</v>
+        <v>528464</v>
       </c>
       <c r="R58" t="n">
-        <v>6937699</v>
+        <v>6937744</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120441066</v>
+        <v>120438833</v>
       </c>
       <c r="B59" t="n">
         <v>97930</v>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528637</v>
+        <v>528539</v>
       </c>
       <c r="R59" t="n">
-        <v>6937690</v>
+        <v>6937677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120441387</v>
+        <v>120437120</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528685</v>
+        <v>528870</v>
       </c>
       <c r="R2" t="n">
-        <v>6937650</v>
+        <v>6937526</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120438560</v>
+        <v>120441461</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528656</v>
+        <v>528743</v>
       </c>
       <c r="R3" t="n">
-        <v>6937598</v>
+        <v>6937610</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120441066</v>
+        <v>120441204</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528637</v>
+        <v>528648</v>
       </c>
       <c r="R4" t="n">
-        <v>6937690</v>
+        <v>6937685</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120439035</v>
+        <v>120439814</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528498</v>
+        <v>528443</v>
       </c>
       <c r="R5" t="n">
-        <v>6937681</v>
+        <v>6937793</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120437120</v>
+        <v>120438853</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528870</v>
+        <v>528547</v>
       </c>
       <c r="R6" t="n">
-        <v>6937526</v>
+        <v>6937670</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120440965</v>
+        <v>120439353</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528632</v>
+        <v>528525</v>
       </c>
       <c r="R7" t="n">
-        <v>6937690</v>
+        <v>6937692</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120437608</v>
+        <v>120441687</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528744</v>
+        <v>528832</v>
       </c>
       <c r="R8" t="n">
-        <v>6937574</v>
+        <v>6937620</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120440885</v>
+        <v>120440522</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528599</v>
+        <v>528469</v>
       </c>
       <c r="R9" t="n">
-        <v>6937706</v>
+        <v>6937757</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120441600</v>
+        <v>120440965</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528802</v>
+        <v>528632</v>
       </c>
       <c r="R10" t="n">
-        <v>6937600</v>
+        <v>6937690</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120438542</v>
+        <v>120440130</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528659</v>
+        <v>528413</v>
       </c>
       <c r="R11" t="n">
-        <v>6937599</v>
+        <v>6937790</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120439129</v>
+        <v>120437716</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528507</v>
+        <v>528697</v>
       </c>
       <c r="R12" t="n">
-        <v>6937686</v>
+        <v>6937605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120440054</v>
+        <v>120439035</v>
       </c>
       <c r="B13" t="n">
-        <v>90972</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,20 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528395</v>
+        <v>528498</v>
       </c>
       <c r="R13" t="n">
-        <v>6937798</v>
+        <v>6937681</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120441265</v>
+        <v>120438845</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528650</v>
+        <v>528539</v>
       </c>
       <c r="R14" t="n">
-        <v>6937679</v>
+        <v>6937680</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2001,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120439210</v>
+        <v>120438542</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528515</v>
+        <v>528659</v>
       </c>
       <c r="R15" t="n">
-        <v>6937709</v>
+        <v>6937599</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120439149</v>
+        <v>120439384</v>
       </c>
       <c r="B16" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528506</v>
+        <v>528516</v>
       </c>
       <c r="R16" t="n">
-        <v>6937698</v>
+        <v>6937699</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120438576</v>
+        <v>120440419</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528646</v>
+        <v>528464</v>
       </c>
       <c r="R17" t="n">
-        <v>6937603</v>
+        <v>6937744</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120440522</v>
+        <v>120439210</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2362,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528469</v>
+        <v>528515</v>
       </c>
       <c r="R18" t="n">
-        <v>6937757</v>
+        <v>6937709</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2409,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120440400</v>
+        <v>120441274</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528463</v>
+        <v>528669</v>
       </c>
       <c r="R19" t="n">
-        <v>6937740</v>
+        <v>6937672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120436956</v>
+        <v>120439563</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2538,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528924</v>
+        <v>528498</v>
       </c>
       <c r="R20" t="n">
-        <v>6937549</v>
+        <v>6937745</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120441204</v>
+        <v>120438963</v>
       </c>
       <c r="B21" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,13 +2668,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528648</v>
+        <v>528506</v>
       </c>
       <c r="R21" t="n">
-        <v>6937685</v>
+        <v>6937684</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2715,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120438853</v>
+        <v>120438646</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2742,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528547</v>
+        <v>528617</v>
       </c>
       <c r="R22" t="n">
-        <v>6937670</v>
+        <v>6937594</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120437570</v>
+        <v>120439804</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>90141</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>937</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,13 +2872,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528747</v>
+        <v>528450</v>
       </c>
       <c r="R23" t="n">
-        <v>6937557</v>
+        <v>6937792</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120438646</v>
+        <v>120438265</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,13 +2974,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528617</v>
+        <v>528695</v>
       </c>
       <c r="R24" t="n">
-        <v>6937594</v>
+        <v>6937599</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3021,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120439384</v>
+        <v>120437190</v>
       </c>
       <c r="B25" t="n">
         <v>79623</v>
@@ -3061,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528516</v>
+        <v>528854</v>
       </c>
       <c r="R25" t="n">
-        <v>6937699</v>
+        <v>6937530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120441284</v>
+        <v>120441538</v>
       </c>
       <c r="B26" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,13 +3178,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528669</v>
+        <v>528764</v>
       </c>
       <c r="R26" t="n">
-        <v>6937668</v>
+        <v>6937612</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3225,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120441461</v>
+        <v>120441974</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,46 +3252,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528743</v>
+        <v>528835</v>
       </c>
       <c r="R27" t="n">
-        <v>6937610</v>
+        <v>6937628</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3332,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120439814</v>
+        <v>120436956</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528443</v>
+        <v>528924</v>
       </c>
       <c r="R28" t="n">
-        <v>6937793</v>
+        <v>6937549</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3434,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120441687</v>
+        <v>120440837</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3456,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528832</v>
+        <v>528564</v>
       </c>
       <c r="R29" t="n">
-        <v>6937620</v>
+        <v>6937735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120440774</v>
+        <v>120439129</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3576,13 +3586,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528513</v>
+        <v>528507</v>
       </c>
       <c r="R30" t="n">
-        <v>6937754</v>
+        <v>6937686</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3638,7 +3648,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120439601</v>
+        <v>120439192</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -3678,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528477</v>
+        <v>528507</v>
       </c>
       <c r="R31" t="n">
-        <v>6937781</v>
+        <v>6937699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120439057</v>
+        <v>120441600</v>
       </c>
       <c r="B32" t="n">
-        <v>5169</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3762,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528492</v>
+        <v>528802</v>
       </c>
       <c r="R32" t="n">
-        <v>6937685</v>
+        <v>6937600</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3816,11 +3826,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3847,7 +3852,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120441274</v>
+        <v>120438876</v>
       </c>
       <c r="B33" t="n">
         <v>79623</v>
@@ -3887,13 +3892,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528669</v>
+        <v>528532</v>
       </c>
       <c r="R33" t="n">
-        <v>6937672</v>
+        <v>6937674</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120437716</v>
+        <v>120439870</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,13 +3994,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528697</v>
+        <v>528452</v>
       </c>
       <c r="R34" t="n">
-        <v>6937605</v>
+        <v>6937837</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120439353</v>
+        <v>120439601</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,42 +4072,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528525</v>
+        <v>528477</v>
       </c>
       <c r="R35" t="n">
-        <v>6937692</v>
+        <v>6937781</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120440938</v>
+        <v>120441066</v>
       </c>
       <c r="B36" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528625</v>
+        <v>528637</v>
       </c>
       <c r="R36" t="n">
-        <v>6937678</v>
+        <v>6937690</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120439368</v>
+        <v>120439057</v>
       </c>
       <c r="B37" t="n">
-        <v>90591</v>
+        <v>5169</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528518</v>
+        <v>528492</v>
       </c>
       <c r="R37" t="n">
-        <v>6937705</v>
+        <v>6937685</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4336,6 +4336,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120439870</v>
+        <v>120440938</v>
       </c>
       <c r="B38" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4374,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,13 +4407,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528452</v>
+        <v>528625</v>
       </c>
       <c r="R38" t="n">
-        <v>6937837</v>
+        <v>6937678</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4464,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120437507</v>
+        <v>120440885</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528761</v>
+        <v>528599</v>
       </c>
       <c r="R39" t="n">
-        <v>6937549</v>
+        <v>6937706</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120438845</v>
+        <v>120441284</v>
       </c>
       <c r="B40" t="n">
         <v>90864</v>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528539</v>
+        <v>528669</v>
       </c>
       <c r="R40" t="n">
-        <v>6937680</v>
+        <v>6937668</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4668,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120441538</v>
+        <v>120438833</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4685,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528764</v>
+        <v>528539</v>
       </c>
       <c r="R41" t="n">
-        <v>6937612</v>
+        <v>6937677</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120440837</v>
+        <v>120439149</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,25 +4787,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528564</v>
+        <v>528506</v>
       </c>
       <c r="R42" t="n">
-        <v>6937735</v>
+        <v>6937698</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120438265</v>
+        <v>120440400</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4889,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528695</v>
+        <v>528463</v>
       </c>
       <c r="R43" t="n">
-        <v>6937599</v>
+        <v>6937740</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120437190</v>
+        <v>120436879</v>
       </c>
       <c r="B44" t="n">
         <v>79623</v>
@@ -5014,13 +5019,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528854</v>
+        <v>528950</v>
       </c>
       <c r="R44" t="n">
-        <v>6937530</v>
+        <v>6937556</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5076,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120440130</v>
+        <v>120441387</v>
       </c>
       <c r="B45" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5093,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,13 +5121,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528413</v>
+        <v>528685</v>
       </c>
       <c r="R45" t="n">
-        <v>6937790</v>
+        <v>6937650</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5178,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120441974</v>
+        <v>120440848</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,25 +5195,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,13 +5223,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528835</v>
+        <v>528571</v>
       </c>
       <c r="R46" t="n">
-        <v>6937628</v>
+        <v>6937738</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5280,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120439563</v>
+        <v>120439927</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,13 +5325,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528498</v>
+        <v>528418</v>
       </c>
       <c r="R47" t="n">
-        <v>6937745</v>
+        <v>6937810</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5382,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120440905</v>
+        <v>120440054</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>90972</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5398,21 +5403,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528612</v>
+        <v>528395</v>
       </c>
       <c r="R48" t="n">
-        <v>6937706</v>
+        <v>6937798</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120440848</v>
+        <v>120438560</v>
       </c>
       <c r="B49" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528571</v>
+        <v>528656</v>
       </c>
       <c r="R49" t="n">
-        <v>6937738</v>
+        <v>6937598</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5586,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120440104</v>
+        <v>120440774</v>
       </c>
       <c r="B50" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5598,25 +5598,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528416</v>
+        <v>528513</v>
       </c>
       <c r="R50" t="n">
-        <v>6937802</v>
+        <v>6937754</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120436879</v>
+        <v>120438911</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5704,21 +5704,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528950</v>
+        <v>528508</v>
       </c>
       <c r="R51" t="n">
-        <v>6937556</v>
+        <v>6937667</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120438876</v>
+        <v>120441265</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5802,25 +5802,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,13 +5830,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528532</v>
+        <v>528650</v>
       </c>
       <c r="R52" t="n">
-        <v>6937674</v>
+        <v>6937679</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120439192</v>
+        <v>120440905</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528507</v>
+        <v>528612</v>
       </c>
       <c r="R53" t="n">
-        <v>6937699</v>
+        <v>6937706</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120438911</v>
+        <v>120438576</v>
       </c>
       <c r="B54" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528508</v>
+        <v>528646</v>
       </c>
       <c r="R54" t="n">
-        <v>6937667</v>
+        <v>6937603</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120438963</v>
+        <v>120437608</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,25 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528506</v>
+        <v>528744</v>
       </c>
       <c r="R55" t="n">
-        <v>6937684</v>
+        <v>6937574</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120439804</v>
+        <v>120437570</v>
       </c>
       <c r="B56" t="n">
-        <v>90141</v>
+        <v>78278</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>937</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,13 +6238,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528450</v>
+        <v>528747</v>
       </c>
       <c r="R56" t="n">
-        <v>6937792</v>
+        <v>6937557</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120439927</v>
+        <v>120437507</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528418</v>
+        <v>528761</v>
       </c>
       <c r="R57" t="n">
-        <v>6937810</v>
+        <v>6937549</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120440419</v>
+        <v>120439368</v>
       </c>
       <c r="B58" t="n">
-        <v>78278</v>
+        <v>90591</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528464</v>
+        <v>528518</v>
       </c>
       <c r="R58" t="n">
-        <v>6937744</v>
+        <v>6937705</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120438833</v>
+        <v>120440104</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6516,25 +6516,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528539</v>
+        <v>528416</v>
       </c>
       <c r="R59" t="n">
-        <v>6937677</v>
+        <v>6937802</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120440130</v>
+        <v>120437716</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528413</v>
+        <v>528697</v>
       </c>
       <c r="R11" t="n">
-        <v>6937790</v>
+        <v>6937605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120437716</v>
+        <v>120440130</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528697</v>
+        <v>528413</v>
       </c>
       <c r="R12" t="n">
-        <v>6937605</v>
+        <v>6937790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120438265</v>
+        <v>120441538</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528695</v>
+        <v>528764</v>
       </c>
       <c r="R24" t="n">
-        <v>6937599</v>
+        <v>6937612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120437190</v>
+        <v>120438265</v>
       </c>
       <c r="B25" t="n">
         <v>79623</v>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528854</v>
+        <v>528695</v>
       </c>
       <c r="R25" t="n">
-        <v>6937530</v>
+        <v>6937599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120441538</v>
+        <v>120437190</v>
       </c>
       <c r="B26" t="n">
         <v>79623</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528764</v>
+        <v>528854</v>
       </c>
       <c r="R26" t="n">
-        <v>6937612</v>
+        <v>6937530</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120436956</v>
+        <v>120440837</v>
       </c>
       <c r="B28" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528924</v>
+        <v>528564</v>
       </c>
       <c r="R28" t="n">
-        <v>6937549</v>
+        <v>6937735</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120440837</v>
+        <v>120439129</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528564</v>
+        <v>528507</v>
       </c>
       <c r="R29" t="n">
-        <v>6937735</v>
+        <v>6937686</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120439129</v>
+        <v>120436956</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,25 +3558,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,13 +3586,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528507</v>
+        <v>528924</v>
       </c>
       <c r="R30" t="n">
-        <v>6937686</v>
+        <v>6937549</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120439601</v>
+        <v>120441066</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,25 +4068,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528477</v>
+        <v>528637</v>
       </c>
       <c r="R35" t="n">
-        <v>6937781</v>
+        <v>6937690</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120441066</v>
+        <v>120439601</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528637</v>
+        <v>528477</v>
       </c>
       <c r="R36" t="n">
-        <v>6937690</v>
+        <v>6937781</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120440885</v>
+        <v>120439149</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528599</v>
+        <v>528506</v>
       </c>
       <c r="R39" t="n">
-        <v>6937706</v>
+        <v>6937698</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120441284</v>
+        <v>120440885</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,13 +4611,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528669</v>
+        <v>528599</v>
       </c>
       <c r="R40" t="n">
-        <v>6937668</v>
+        <v>6937706</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120438833</v>
+        <v>120441284</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528539</v>
+        <v>528669</v>
       </c>
       <c r="R41" t="n">
-        <v>6937677</v>
+        <v>6937668</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120439149</v>
+        <v>120438833</v>
       </c>
       <c r="B42" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,25 +4787,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528506</v>
+        <v>528539</v>
       </c>
       <c r="R42" t="n">
-        <v>6937698</v>
+        <v>6937677</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120437120</v>
+        <v>120441265</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528870</v>
+        <v>528650</v>
       </c>
       <c r="R2" t="n">
-        <v>6937526</v>
+        <v>6937679</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120441461</v>
+        <v>120438542</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528743</v>
+        <v>528659</v>
       </c>
       <c r="R3" t="n">
-        <v>6937610</v>
+        <v>6937599</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120441204</v>
+        <v>120441974</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528648</v>
+        <v>528835</v>
       </c>
       <c r="R4" t="n">
-        <v>6937685</v>
+        <v>6937628</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120439814</v>
+        <v>120441600</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528443</v>
+        <v>528802</v>
       </c>
       <c r="R5" t="n">
-        <v>6937793</v>
+        <v>6937600</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120438853</v>
+        <v>120439601</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528547</v>
+        <v>528477</v>
       </c>
       <c r="R6" t="n">
-        <v>6937670</v>
+        <v>6937781</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120439353</v>
+        <v>120439384</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,42 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528525</v>
+        <v>528516</v>
       </c>
       <c r="R7" t="n">
-        <v>6937692</v>
+        <v>6937699</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120441687</v>
+        <v>120438845</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528832</v>
+        <v>528539</v>
       </c>
       <c r="R8" t="n">
-        <v>6937620</v>
+        <v>6937680</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120440522</v>
+        <v>120440885</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528469</v>
+        <v>528599</v>
       </c>
       <c r="R9" t="n">
-        <v>6937757</v>
+        <v>6937706</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120440965</v>
+        <v>120441284</v>
       </c>
       <c r="B10" t="n">
         <v>90864</v>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528632</v>
+        <v>528669</v>
       </c>
       <c r="R10" t="n">
-        <v>6937690</v>
+        <v>6937668</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120437716</v>
+        <v>120438576</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1643,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528697</v>
+        <v>528646</v>
       </c>
       <c r="R11" t="n">
-        <v>6937605</v>
+        <v>6937603</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120440130</v>
+        <v>120437190</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528413</v>
+        <v>528854</v>
       </c>
       <c r="R12" t="n">
-        <v>6937790</v>
+        <v>6937530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120439035</v>
+        <v>120441538</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528498</v>
+        <v>528764</v>
       </c>
       <c r="R13" t="n">
-        <v>6937681</v>
+        <v>6937612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120438845</v>
+        <v>120439814</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528539</v>
+        <v>528443</v>
       </c>
       <c r="R14" t="n">
-        <v>6937680</v>
+        <v>6937793</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120438542</v>
+        <v>120438560</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2056,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528659</v>
+        <v>528656</v>
       </c>
       <c r="R15" t="n">
-        <v>6937599</v>
+        <v>6937598</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120439384</v>
+        <v>120439035</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528516</v>
+        <v>528498</v>
       </c>
       <c r="R16" t="n">
-        <v>6937699</v>
+        <v>6937681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2179,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120440419</v>
+        <v>120436879</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528464</v>
+        <v>528950</v>
       </c>
       <c r="R17" t="n">
-        <v>6937744</v>
+        <v>6937556</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120439210</v>
+        <v>120440837</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528515</v>
+        <v>528564</v>
       </c>
       <c r="R18" t="n">
-        <v>6937709</v>
+        <v>6937735</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120441274</v>
+        <v>120439129</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528669</v>
+        <v>528507</v>
       </c>
       <c r="R19" t="n">
-        <v>6937672</v>
+        <v>6937686</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120439563</v>
+        <v>120439927</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528498</v>
+        <v>528418</v>
       </c>
       <c r="R20" t="n">
-        <v>6937745</v>
+        <v>6937810</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120438963</v>
+        <v>120438265</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528506</v>
+        <v>528695</v>
       </c>
       <c r="R21" t="n">
-        <v>6937684</v>
+        <v>6937599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120438646</v>
+        <v>120441687</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528617</v>
+        <v>528832</v>
       </c>
       <c r="R22" t="n">
-        <v>6937594</v>
+        <v>6937620</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2832,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120439804</v>
+        <v>120440522</v>
       </c>
       <c r="B23" t="n">
-        <v>90141</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>937</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528450</v>
+        <v>528469</v>
       </c>
       <c r="R23" t="n">
-        <v>6937792</v>
+        <v>6937757</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2934,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120441538</v>
+        <v>120441461</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,37 +2940,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528764</v>
+        <v>528743</v>
       </c>
       <c r="R24" t="n">
-        <v>6937612</v>
+        <v>6937610</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3036,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120438265</v>
+        <v>120437120</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528695</v>
+        <v>528870</v>
       </c>
       <c r="R25" t="n">
-        <v>6937599</v>
+        <v>6937526</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3138,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120437190</v>
+        <v>120440419</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528854</v>
+        <v>528464</v>
       </c>
       <c r="R26" t="n">
-        <v>6937530</v>
+        <v>6937744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120441974</v>
+        <v>120440104</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528835</v>
+        <v>528416</v>
       </c>
       <c r="R27" t="n">
-        <v>6937628</v>
+        <v>6937802</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3342,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120440837</v>
+        <v>120441274</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528564</v>
+        <v>528669</v>
       </c>
       <c r="R28" t="n">
-        <v>6937735</v>
+        <v>6937672</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120439129</v>
+        <v>120438853</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3484,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528507</v>
+        <v>528547</v>
       </c>
       <c r="R29" t="n">
-        <v>6937686</v>
+        <v>6937670</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3546,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120436956</v>
+        <v>120440938</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>91023</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,13 +3581,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528924</v>
+        <v>528625</v>
       </c>
       <c r="R30" t="n">
-        <v>6937549</v>
+        <v>6937678</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3648,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120439192</v>
+        <v>120438646</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,13 +3683,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528507</v>
+        <v>528617</v>
       </c>
       <c r="R31" t="n">
-        <v>6937699</v>
+        <v>6937594</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3750,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120441600</v>
+        <v>120440130</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,13 +3785,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528802</v>
+        <v>528413</v>
       </c>
       <c r="R32" t="n">
-        <v>6937600</v>
+        <v>6937790</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3852,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120438876</v>
+        <v>120437716</v>
       </c>
       <c r="B33" t="n">
         <v>79623</v>
@@ -3892,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528532</v>
+        <v>528697</v>
       </c>
       <c r="R33" t="n">
-        <v>6937674</v>
+        <v>6937605</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3954,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120439870</v>
+        <v>120439057</v>
       </c>
       <c r="B34" t="n">
-        <v>90864</v>
+        <v>5169</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3966,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528452</v>
+        <v>528492</v>
       </c>
       <c r="R34" t="n">
-        <v>6937837</v>
+        <v>6937685</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4030,6 +4025,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4056,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120441066</v>
+        <v>120440054</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>90972</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,25 +4068,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4096,13 +4091,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528637</v>
+        <v>528395</v>
       </c>
       <c r="R35" t="n">
-        <v>6937690</v>
+        <v>6937798</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120439601</v>
+        <v>120438833</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4170,25 +4165,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528477</v>
+        <v>528539</v>
       </c>
       <c r="R36" t="n">
-        <v>6937781</v>
+        <v>6937677</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120439057</v>
+        <v>120441066</v>
       </c>
       <c r="B37" t="n">
-        <v>5169</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4272,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4300,13 +4295,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528492</v>
+        <v>528637</v>
       </c>
       <c r="R37" t="n">
-        <v>6937685</v>
+        <v>6937690</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4336,11 +4331,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4367,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120440938</v>
+        <v>120438963</v>
       </c>
       <c r="B38" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,21 +4373,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528625</v>
+        <v>528506</v>
       </c>
       <c r="R38" t="n">
-        <v>6937678</v>
+        <v>6937684</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4459,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120439149</v>
+        <v>120441204</v>
       </c>
       <c r="B39" t="n">
         <v>95478</v>
@@ -4509,13 +4499,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528506</v>
+        <v>528648</v>
       </c>
       <c r="R39" t="n">
-        <v>6937698</v>
+        <v>6937685</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4571,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120440885</v>
+        <v>120440905</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,13 +4601,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528599</v>
+        <v>528612</v>
       </c>
       <c r="R40" t="n">
         <v>6937706</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4673,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120441284</v>
+        <v>120437570</v>
       </c>
       <c r="B41" t="n">
-        <v>90864</v>
+        <v>78278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528669</v>
+        <v>528747</v>
       </c>
       <c r="R41" t="n">
-        <v>6937668</v>
+        <v>6937557</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4775,7 +4765,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120438833</v>
+        <v>120439563</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -4815,13 +4805,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528539</v>
+        <v>528498</v>
       </c>
       <c r="R42" t="n">
-        <v>6937677</v>
+        <v>6937745</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4877,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120440400</v>
+        <v>120440848</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>90864</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4889,25 +4879,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,13 +4907,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528463</v>
+        <v>528571</v>
       </c>
       <c r="R43" t="n">
-        <v>6937740</v>
+        <v>6937738</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120436879</v>
+        <v>120439149</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>95478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,13 +5009,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528950</v>
+        <v>528506</v>
       </c>
       <c r="R44" t="n">
-        <v>6937556</v>
+        <v>6937698</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5081,10 +5071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120441387</v>
+        <v>120439804</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>90141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5093,25 +5083,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>937</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,13 +5111,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528685</v>
+        <v>528450</v>
       </c>
       <c r="R45" t="n">
-        <v>6937650</v>
+        <v>6937792</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5183,10 +5173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120440848</v>
+        <v>120439353</v>
       </c>
       <c r="B46" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,37 +5189,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528571</v>
+        <v>528525</v>
       </c>
       <c r="R46" t="n">
-        <v>6937738</v>
+        <v>6937692</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5285,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120439927</v>
+        <v>120437507</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,21 +5296,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,13 +5320,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528418</v>
+        <v>528761</v>
       </c>
       <c r="R47" t="n">
-        <v>6937810</v>
+        <v>6937549</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5387,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120440054</v>
+        <v>120439368</v>
       </c>
       <c r="B48" t="n">
-        <v>90972</v>
+        <v>90591</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,20 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528395</v>
+        <v>528518</v>
       </c>
       <c r="R48" t="n">
-        <v>6937798</v>
+        <v>6937705</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120438560</v>
+        <v>120436956</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528656</v>
+        <v>528924</v>
       </c>
       <c r="R49" t="n">
-        <v>6937598</v>
+        <v>6937549</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5586,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120440774</v>
+        <v>120437608</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5598,25 +5598,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528513</v>
+        <v>528744</v>
       </c>
       <c r="R50" t="n">
-        <v>6937754</v>
+        <v>6937574</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120438911</v>
+        <v>120440774</v>
       </c>
       <c r="B51" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528508</v>
+        <v>528513</v>
       </c>
       <c r="R51" t="n">
-        <v>6937667</v>
+        <v>6937754</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120441265</v>
+        <v>120438911</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5802,25 +5802,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,13 +5830,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528650</v>
+        <v>528508</v>
       </c>
       <c r="R52" t="n">
-        <v>6937679</v>
+        <v>6937667</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120440905</v>
+        <v>120438876</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528612</v>
+        <v>528532</v>
       </c>
       <c r="R53" t="n">
-        <v>6937706</v>
+        <v>6937674</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5994,7 +5994,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120438576</v>
+        <v>120439192</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528646</v>
+        <v>528507</v>
       </c>
       <c r="R54" t="n">
-        <v>6937603</v>
+        <v>6937699</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120437608</v>
+        <v>120441387</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,25 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528744</v>
+        <v>528685</v>
       </c>
       <c r="R55" t="n">
-        <v>6937574</v>
+        <v>6937650</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120437570</v>
+        <v>120439210</v>
       </c>
       <c r="B56" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528747</v>
+        <v>528515</v>
       </c>
       <c r="R56" t="n">
-        <v>6937557</v>
+        <v>6937709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120437507</v>
+        <v>120440965</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528761</v>
+        <v>528632</v>
       </c>
       <c r="R57" t="n">
-        <v>6937549</v>
+        <v>6937690</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120439368</v>
+        <v>120439870</v>
       </c>
       <c r="B58" t="n">
-        <v>90591</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528518</v>
+        <v>528452</v>
       </c>
       <c r="R58" t="n">
-        <v>6937705</v>
+        <v>6937837</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120440104</v>
+        <v>120440400</v>
       </c>
       <c r="B59" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6516,25 +6516,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528416</v>
+        <v>528463</v>
       </c>
       <c r="R59" t="n">
-        <v>6937802</v>
+        <v>6937740</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120441265</v>
+        <v>120438265</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528650</v>
+        <v>528695</v>
       </c>
       <c r="R2" t="n">
-        <v>6937679</v>
+        <v>6937599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120438542</v>
+        <v>120439601</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528659</v>
+        <v>528477</v>
       </c>
       <c r="R3" t="n">
-        <v>6937599</v>
+        <v>6937781</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120441974</v>
+        <v>120440885</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528835</v>
+        <v>528599</v>
       </c>
       <c r="R4" t="n">
-        <v>6937628</v>
+        <v>6937706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120441600</v>
+        <v>120437608</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528802</v>
+        <v>528744</v>
       </c>
       <c r="R5" t="n">
-        <v>6937600</v>
+        <v>6937574</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120439601</v>
+        <v>120441538</v>
       </c>
       <c r="B6" t="n">
         <v>79623</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528477</v>
+        <v>528764</v>
       </c>
       <c r="R6" t="n">
-        <v>6937781</v>
+        <v>6937612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120439384</v>
+        <v>120438876</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528516</v>
+        <v>528532</v>
       </c>
       <c r="R7" t="n">
-        <v>6937699</v>
+        <v>6937674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120438845</v>
+        <v>120439149</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>95478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528539</v>
+        <v>528506</v>
       </c>
       <c r="R8" t="n">
-        <v>6937680</v>
+        <v>6937698</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120440885</v>
+        <v>120438646</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528599</v>
+        <v>528617</v>
       </c>
       <c r="R9" t="n">
-        <v>6937706</v>
+        <v>6937594</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120441284</v>
+        <v>120438833</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528669</v>
+        <v>528539</v>
       </c>
       <c r="R10" t="n">
-        <v>6937668</v>
+        <v>6937677</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120438576</v>
+        <v>120440837</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528646</v>
+        <v>528564</v>
       </c>
       <c r="R11" t="n">
-        <v>6937603</v>
+        <v>6937735</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120437190</v>
+        <v>120440419</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528854</v>
+        <v>528464</v>
       </c>
       <c r="R12" t="n">
-        <v>6937530</v>
+        <v>6937744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120441538</v>
+        <v>120441600</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528764</v>
+        <v>528802</v>
       </c>
       <c r="R13" t="n">
-        <v>6937612</v>
+        <v>6937600</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120439814</v>
+        <v>120438911</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528443</v>
+        <v>528508</v>
       </c>
       <c r="R14" t="n">
-        <v>6937793</v>
+        <v>6937667</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120438560</v>
+        <v>120440130</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528656</v>
+        <v>528413</v>
       </c>
       <c r="R15" t="n">
-        <v>6937598</v>
+        <v>6937790</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120436879</v>
+        <v>120441461</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,37 +2226,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528950</v>
+        <v>528743</v>
       </c>
       <c r="R17" t="n">
-        <v>6937556</v>
+        <v>6937610</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120440837</v>
+        <v>120437507</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528564</v>
+        <v>528761</v>
       </c>
       <c r="R18" t="n">
-        <v>6937735</v>
+        <v>6937549</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120439129</v>
+        <v>120440938</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528507</v>
+        <v>528625</v>
       </c>
       <c r="R19" t="n">
-        <v>6937686</v>
+        <v>6937678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120439927</v>
+        <v>120437570</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528418</v>
+        <v>528747</v>
       </c>
       <c r="R20" t="n">
-        <v>6937810</v>
+        <v>6937557</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120438265</v>
+        <v>120438845</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2663,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528695</v>
+        <v>528539</v>
       </c>
       <c r="R21" t="n">
-        <v>6937599</v>
+        <v>6937680</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120441687</v>
+        <v>120440848</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528832</v>
+        <v>528571</v>
       </c>
       <c r="R22" t="n">
-        <v>6937620</v>
+        <v>6937738</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120440522</v>
+        <v>120439384</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2867,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528469</v>
+        <v>528516</v>
       </c>
       <c r="R23" t="n">
-        <v>6937757</v>
+        <v>6937699</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120441461</v>
+        <v>120439353</v>
       </c>
       <c r="B24" t="n">
         <v>57473</v>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528743</v>
+        <v>528525</v>
       </c>
       <c r="R24" t="n">
-        <v>6937610</v>
+        <v>6937692</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3031,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120437120</v>
+        <v>120440905</v>
       </c>
       <c r="B25" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528870</v>
+        <v>528612</v>
       </c>
       <c r="R25" t="n">
-        <v>6937526</v>
+        <v>6937706</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120440419</v>
+        <v>120440054</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>90972</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3154,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528464</v>
+        <v>528395</v>
       </c>
       <c r="R26" t="n">
-        <v>6937744</v>
+        <v>6937798</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120440104</v>
+        <v>120439368</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>90591</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528416</v>
+        <v>528518</v>
       </c>
       <c r="R27" t="n">
-        <v>6937802</v>
+        <v>6937705</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120441274</v>
+        <v>120437190</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528669</v>
+        <v>528854</v>
       </c>
       <c r="R28" t="n">
-        <v>6937672</v>
+        <v>6937530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120438853</v>
+        <v>120440522</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528547</v>
+        <v>528469</v>
       </c>
       <c r="R29" t="n">
-        <v>6937670</v>
+        <v>6937757</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120440938</v>
+        <v>120438542</v>
       </c>
       <c r="B30" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528625</v>
+        <v>528659</v>
       </c>
       <c r="R30" t="n">
-        <v>6937678</v>
+        <v>6937599</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120438646</v>
+        <v>120441066</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528617</v>
+        <v>528637</v>
       </c>
       <c r="R31" t="n">
-        <v>6937594</v>
+        <v>6937690</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120440130</v>
+        <v>120438963</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528413</v>
+        <v>528506</v>
       </c>
       <c r="R32" t="n">
-        <v>6937790</v>
+        <v>6937684</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120437716</v>
+        <v>120437120</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528697</v>
+        <v>528870</v>
       </c>
       <c r="R33" t="n">
-        <v>6937605</v>
+        <v>6937526</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120439057</v>
+        <v>120439870</v>
       </c>
       <c r="B34" t="n">
-        <v>5169</v>
+        <v>90864</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528492</v>
+        <v>528452</v>
       </c>
       <c r="R34" t="n">
-        <v>6937685</v>
+        <v>6937837</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4025,11 +4025,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4056,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120440054</v>
+        <v>120440400</v>
       </c>
       <c r="B35" t="n">
-        <v>90972</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,20 +4063,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528395</v>
+        <v>528463</v>
       </c>
       <c r="R35" t="n">
-        <v>6937798</v>
+        <v>6937740</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120438833</v>
+        <v>120438560</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4193,13 +4193,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528539</v>
+        <v>528656</v>
       </c>
       <c r="R36" t="n">
-        <v>6937677</v>
+        <v>6937598</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120441066</v>
+        <v>120440774</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528637</v>
+        <v>528513</v>
       </c>
       <c r="R37" t="n">
-        <v>6937690</v>
+        <v>6937754</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120438963</v>
+        <v>120441974</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528506</v>
+        <v>528835</v>
       </c>
       <c r="R38" t="n">
-        <v>6937684</v>
+        <v>6937628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120441204</v>
+        <v>120441274</v>
       </c>
       <c r="B39" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,13 +4499,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528648</v>
+        <v>528669</v>
       </c>
       <c r="R39" t="n">
-        <v>6937685</v>
+        <v>6937672</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120440905</v>
+        <v>120441687</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528612</v>
+        <v>528832</v>
       </c>
       <c r="R40" t="n">
-        <v>6937706</v>
+        <v>6937620</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120437570</v>
+        <v>120441265</v>
       </c>
       <c r="B41" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528747</v>
+        <v>528650</v>
       </c>
       <c r="R41" t="n">
-        <v>6937557</v>
+        <v>6937679</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120439563</v>
+        <v>120439210</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4777,25 +4777,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528498</v>
+        <v>528515</v>
       </c>
       <c r="R42" t="n">
-        <v>6937745</v>
+        <v>6937709</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120440848</v>
+        <v>120439057</v>
       </c>
       <c r="B43" t="n">
-        <v>90864</v>
+        <v>5169</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528571</v>
+        <v>528492</v>
       </c>
       <c r="R43" t="n">
-        <v>6937738</v>
+        <v>6937685</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4943,6 +4943,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4969,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120439149</v>
+        <v>120438853</v>
       </c>
       <c r="B44" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4981,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5009,13 +5014,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528506</v>
+        <v>528547</v>
       </c>
       <c r="R44" t="n">
-        <v>6937698</v>
+        <v>6937670</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5071,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120439804</v>
+        <v>120441204</v>
       </c>
       <c r="B45" t="n">
-        <v>90141</v>
+        <v>95478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5087,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>937</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528450</v>
+        <v>528648</v>
       </c>
       <c r="R45" t="n">
-        <v>6937792</v>
+        <v>6937685</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5173,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120439353</v>
+        <v>120439814</v>
       </c>
       <c r="B46" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5189,42 +5194,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Finnberget, Finnberget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528525</v>
+        <v>528443</v>
       </c>
       <c r="R46" t="n">
-        <v>6937692</v>
+        <v>6937793</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120437507</v>
+        <v>120441387</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,13 +5320,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528761</v>
+        <v>528685</v>
       </c>
       <c r="R47" t="n">
-        <v>6937549</v>
+        <v>6937650</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5382,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120439368</v>
+        <v>120436956</v>
       </c>
       <c r="B48" t="n">
-        <v>90591</v>
+        <v>78278</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528518</v>
+        <v>528924</v>
       </c>
       <c r="R48" t="n">
-        <v>6937705</v>
+        <v>6937549</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120436956</v>
+        <v>120438576</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5500,21 +5500,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528924</v>
+        <v>528646</v>
       </c>
       <c r="R49" t="n">
-        <v>6937549</v>
+        <v>6937603</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5586,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120437608</v>
+        <v>120437716</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5598,25 +5598,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5626,13 +5626,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528744</v>
+        <v>528697</v>
       </c>
       <c r="R50" t="n">
-        <v>6937574</v>
+        <v>6937605</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120440774</v>
+        <v>120439192</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,13 +5728,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528513</v>
+        <v>528507</v>
       </c>
       <c r="R51" t="n">
-        <v>6937754</v>
+        <v>6937699</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120438911</v>
+        <v>120439804</v>
       </c>
       <c r="B52" t="n">
-        <v>90864</v>
+        <v>90141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5806,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>937</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528508</v>
+        <v>528450</v>
       </c>
       <c r="R52" t="n">
-        <v>6937667</v>
+        <v>6937792</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120438876</v>
+        <v>120439129</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5904,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528532</v>
+        <v>528507</v>
       </c>
       <c r="R53" t="n">
-        <v>6937674</v>
+        <v>6937686</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120439192</v>
+        <v>120439927</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528507</v>
+        <v>528418</v>
       </c>
       <c r="R54" t="n">
-        <v>6937699</v>
+        <v>6937810</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120441387</v>
+        <v>120440965</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,25 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528685</v>
+        <v>528632</v>
       </c>
       <c r="R55" t="n">
-        <v>6937650</v>
+        <v>6937690</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120439210</v>
+        <v>120439563</v>
       </c>
       <c r="B56" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6210,25 +6210,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,13 +6238,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528515</v>
+        <v>528498</v>
       </c>
       <c r="R56" t="n">
-        <v>6937709</v>
+        <v>6937745</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120440965</v>
+        <v>120440104</v>
       </c>
       <c r="B57" t="n">
         <v>90864</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528632</v>
+        <v>528416</v>
       </c>
       <c r="R57" t="n">
-        <v>6937690</v>
+        <v>6937802</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120439870</v>
+        <v>120441284</v>
       </c>
       <c r="B58" t="n">
         <v>90864</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528452</v>
+        <v>528669</v>
       </c>
       <c r="R58" t="n">
-        <v>6937837</v>
+        <v>6937668</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120440400</v>
+        <v>120436879</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6516,25 +6516,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528463</v>
+        <v>528950</v>
       </c>
       <c r="R59" t="n">
-        <v>6937740</v>
+        <v>6937556</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120438265</v>
+        <v>120439601</v>
       </c>
       <c r="B2" t="n">
         <v>79623</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528695</v>
+        <v>528477</v>
       </c>
       <c r="R2" t="n">
-        <v>6937599</v>
+        <v>6937781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120439601</v>
+        <v>120438265</v>
       </c>
       <c r="B3" t="n">
         <v>79623</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528477</v>
+        <v>528695</v>
       </c>
       <c r="R3" t="n">
-        <v>6937781</v>
+        <v>6937599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120441538</v>
+        <v>120439149</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>95478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528764</v>
+        <v>528506</v>
       </c>
       <c r="R6" t="n">
-        <v>6937612</v>
+        <v>6937698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120438876</v>
+        <v>120438646</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528532</v>
+        <v>528617</v>
       </c>
       <c r="R7" t="n">
-        <v>6937674</v>
+        <v>6937594</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120439149</v>
+        <v>120441538</v>
       </c>
       <c r="B8" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528506</v>
+        <v>528764</v>
       </c>
       <c r="R8" t="n">
-        <v>6937698</v>
+        <v>6937612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120438646</v>
+        <v>120438876</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528617</v>
+        <v>528532</v>
       </c>
       <c r="R9" t="n">
-        <v>6937594</v>
+        <v>6937674</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120437507</v>
+        <v>120437570</v>
       </c>
       <c r="B18" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528761</v>
+        <v>528747</v>
       </c>
       <c r="R18" t="n">
-        <v>6937549</v>
+        <v>6937557</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120440938</v>
+        <v>120438845</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528625</v>
+        <v>528539</v>
       </c>
       <c r="R19" t="n">
-        <v>6937678</v>
+        <v>6937680</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120437570</v>
+        <v>120440848</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528747</v>
+        <v>528571</v>
       </c>
       <c r="R20" t="n">
-        <v>6937557</v>
+        <v>6937738</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120438845</v>
+        <v>120437507</v>
       </c>
       <c r="B21" t="n">
-        <v>90864</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528539</v>
+        <v>528761</v>
       </c>
       <c r="R21" t="n">
-        <v>6937680</v>
+        <v>6937549</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120440848</v>
+        <v>120440938</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528571</v>
+        <v>528625</v>
       </c>
       <c r="R22" t="n">
-        <v>6937738</v>
+        <v>6937678</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120437190</v>
+        <v>120438542</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528854</v>
+        <v>528659</v>
       </c>
       <c r="R28" t="n">
-        <v>6937530</v>
+        <v>6937599</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120440522</v>
+        <v>120441066</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528469</v>
+        <v>528637</v>
       </c>
       <c r="R29" t="n">
-        <v>6937757</v>
+        <v>6937690</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120438542</v>
+        <v>120438963</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528659</v>
+        <v>528506</v>
       </c>
       <c r="R30" t="n">
-        <v>6937599</v>
+        <v>6937684</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120441066</v>
+        <v>120437120</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528637</v>
+        <v>528870</v>
       </c>
       <c r="R31" t="n">
-        <v>6937690</v>
+        <v>6937526</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120438963</v>
+        <v>120440522</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528506</v>
+        <v>528469</v>
       </c>
       <c r="R32" t="n">
-        <v>6937684</v>
+        <v>6937757</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120437120</v>
+        <v>120437190</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528870</v>
+        <v>528854</v>
       </c>
       <c r="R33" t="n">
-        <v>6937526</v>
+        <v>6937530</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120439814</v>
+        <v>120436956</v>
       </c>
       <c r="B46" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528443</v>
+        <v>528924</v>
       </c>
       <c r="R46" t="n">
-        <v>6937793</v>
+        <v>6937549</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120441387</v>
+        <v>120439814</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,13 +5320,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528685</v>
+        <v>528443</v>
       </c>
       <c r="R47" t="n">
-        <v>6937650</v>
+        <v>6937793</v>
       </c>
       <c r="S47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5382,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120436956</v>
+        <v>120441387</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528924</v>
+        <v>528685</v>
       </c>
       <c r="R48" t="n">
-        <v>6937549</v>
+        <v>6937650</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120438576</v>
+        <v>120439129</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528646</v>
+        <v>528507</v>
       </c>
       <c r="R49" t="n">
-        <v>6937603</v>
+        <v>6937686</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120437716</v>
+        <v>120438576</v>
       </c>
       <c r="B50" t="n">
         <v>79623</v>
@@ -5626,13 +5626,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528697</v>
+        <v>528646</v>
       </c>
       <c r="R50" t="n">
-        <v>6937605</v>
+        <v>6937603</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120439192</v>
+        <v>120437716</v>
       </c>
       <c r="B51" t="n">
         <v>79623</v>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528507</v>
+        <v>528697</v>
       </c>
       <c r="R51" t="n">
-        <v>6937699</v>
+        <v>6937605</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120439804</v>
+        <v>120439192</v>
       </c>
       <c r="B52" t="n">
-        <v>90141</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5806,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,13 +5830,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528450</v>
+        <v>528507</v>
       </c>
       <c r="R52" t="n">
-        <v>6937792</v>
+        <v>6937699</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120439129</v>
+        <v>120439804</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>90141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5904,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>937</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528507</v>
+        <v>528450</v>
       </c>
       <c r="R53" t="n">
-        <v>6937686</v>
+        <v>6937792</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120440104</v>
+        <v>120436879</v>
       </c>
       <c r="B57" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528416</v>
+        <v>528950</v>
       </c>
       <c r="R57" t="n">
-        <v>6937802</v>
+        <v>6937556</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120441284</v>
+        <v>120440104</v>
       </c>
       <c r="B58" t="n">
         <v>90864</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528669</v>
+        <v>528416</v>
       </c>
       <c r="R58" t="n">
-        <v>6937668</v>
+        <v>6937802</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120436879</v>
+        <v>120441284</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6520,21 +6520,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528950</v>
+        <v>528669</v>
       </c>
       <c r="R59" t="n">
-        <v>6937556</v>
+        <v>6937668</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 54677-2023 artfynd.xlsx
+++ b/artfynd/A 54677-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438646</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438845</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438911</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439210</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439870</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440104</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440848</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440965</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441284</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439804</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440885</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439368</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440938</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437608</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440400</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440522</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438853</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120436956</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437570</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440419</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441687</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120436879</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437190</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437716</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438265</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438576</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438876</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439192</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439384</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439601</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439814</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439927</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440905</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441274</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441538</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441600</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4685,6 +4890,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831596</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4808,6 +5018,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79079087</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4910,6 +5125,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439057</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5012,6 +5232,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439353</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5114,6 +5339,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441461</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5211,6 +5441,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438542</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5308,6 +5543,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438560</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5405,6 +5645,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438833</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5502,6 +5747,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438963</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5604,6 +5854,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439035</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5701,6 +5956,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439129</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5798,6 +6058,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439563</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5895,6 +6160,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440774</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5992,6 +6262,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440837</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6089,6 +6364,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441066</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6186,6 +6466,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441265</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6283,6 +6568,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441387</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6380,6 +6670,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441974</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6477,6 +6772,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437120</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6574,8 +6874,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>